--- a/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
+++ b/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_455D22EEA74B49281F2C4C488DE931357979617D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25FDE7FA-627C-4569-A679-CBFFD3026AB0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353276C5-2276-4E7B-8E4B-4D2158548C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30975" yWindow="11490" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1068,6 +1068,44 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1096,44 +1134,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1148,20 +1148,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F28BB66-5809-488D-8CE6-5CE10F3DC47B}" name="Table1" displayName="Table1" ref="A1:H217" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F28BB66-5809-488D-8CE6-5CE10F3DC47B}" name="Table1" displayName="Table1" ref="A1:H217" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
   <autoFilter ref="A1:H217" xr:uid="{8F28BB66-5809-488D-8CE6-5CE10F3DC47B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H217">
     <sortCondition ref="C1:C217"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4D5BA935-6B01-4B0A-A94B-B08A45D74ACF}" name="Departments" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{C5C51A37-B7D4-447E-8F1F-63799C4F6030}" name="Year:" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{EB505041-91A7-4B30-A563-DFFFF368ECD0}" name="Course ID" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{13362E5F-035B-4B10-9B19-2A4DE8794AFA}" name="Day" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{60828F31-6DC1-4623-87D8-2A593E0F2D2A}" name="Assigned Rooms" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{CA559115-2440-46B5-9225-FF71C86872C5}" name="Num Rooms Used" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{1CF2E99D-6496-4A2B-86BE-6EEC28AA4BAF}" name="Total Room Cap" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{5D62E8FD-0DC1-4595-879C-44EC1DC3AC05}" name="Num Students" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{4D5BA935-6B01-4B0A-A94B-B08A45D74ACF}" name="Departments" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C5C51A37-B7D4-447E-8F1F-63799C4F6030}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{EB505041-91A7-4B30-A563-DFFFF368ECD0}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{13362E5F-035B-4B10-9B19-2A4DE8794AFA}" name="Day" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{60828F31-6DC1-4623-87D8-2A593E0F2D2A}" name="Assigned Rooms" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{CA559115-2440-46B5-9225-FF71C86872C5}" name="Num Rooms Used" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{1CF2E99D-6496-4A2B-86BE-6EEC28AA4BAF}" name="Total Room Cap" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{5D62E8FD-0DC1-4595-879C-44EC1DC3AC05}" name="Num Students" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1455,17 +1455,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H217"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.265625" customWidth="1"/>
-    <col min="6" max="6" width="17.46484375" customWidth="1"/>
-    <col min="7" max="7" width="15.59765625" customWidth="1"/>
-    <col min="8" max="8" width="14.53125" customWidth="1"/>
+    <col min="1" max="1" width="13.6328125" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>8</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>8</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>8</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>14</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>14</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>14</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>14</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>14</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>14</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>14</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>12</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>12</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>12</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>12</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>12</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>12</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>12</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>12</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>12</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>12</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>12</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>12</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>12</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>12</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>12</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>12</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>18</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>11</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>11</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>11</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>11</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>11</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>11</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>11</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>11</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>11</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>11</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>11</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>11</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>11</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>11</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>11</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>11</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>11</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>11</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>11</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>11</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>11</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>11</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>9</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>9</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>9</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>15</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>9</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>9</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>9</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>9</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>9</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>9</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>9</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>9</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>9</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>9</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>9</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>9</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>9</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>9</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>9</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>9</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>9</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>9</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>9</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>9</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>9</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>10</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>10</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>10</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>10</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>10</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>10</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>10</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>10</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>10</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>10</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>10</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>10</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>10</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>10</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>10</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>10</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>10</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>10</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>8</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>16</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>11</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>13</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>13</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>13</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>13</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>13</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>13</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>13</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>13</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>13</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>13</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>13</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>13</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>13</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>13</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>13</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>13</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>13</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>13</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>13</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>13</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>13</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>13</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>13</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>13</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>13</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>13</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>13</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>13</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>13</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>13</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>13</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>13</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>13</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>13</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>13</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>13</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>8</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>17</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>15</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>11</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>13</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>8</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>13</v>
       </c>

--- a/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
+++ b/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353276C5-2276-4E7B-8E4B-4D2158548C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB858EF-1756-4B2F-884F-4E870F4EF3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30975" yWindow="11490" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35520" yWindow="13725" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <t>Departments</t>
   </si>
   <si>
-    <t>Year:</t>
-  </si>
-  <si>
     <t>Course ID</t>
   </si>
   <si>
@@ -995,6 +992,9 @@
   </si>
   <si>
     <t>['Amfi 4', 'BB01', 'BB04']</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1155,7 @@
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4D5BA935-6B01-4B0A-A94B-B08A45D74ACF}" name="Departments" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{C5C51A37-B7D4-447E-8F1F-63799C4F6030}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C5C51A37-B7D4-447E-8F1F-63799C4F6030}" name="Year" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{EB505041-91A7-4B30-A563-DFFFF368ECD0}" name="Course ID" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{13362E5F-035B-4B10-9B19-2A4DE8794AFA}" name="Day" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{60828F31-6DC1-4623-87D8-2A593E0F2D2A}" name="Assigned Rooms" dataDxfId="3"/>
@@ -1470,42 +1470,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F2" s="2">
         <v>4</v>
@@ -1519,19 +1519,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -1545,19 +1545,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2">
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F4" s="2">
         <v>4</v>
@@ -1571,19 +1571,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -1597,19 +1597,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -1623,19 +1623,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
@@ -1649,19 +1649,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F8" s="2">
         <v>2</v>
@@ -1675,19 +1675,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F10" s="2">
         <v>1</v>
@@ -1727,19 +1727,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F11" s="2">
         <v>2</v>
@@ -1753,19 +1753,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1831,19 +1831,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1857,19 +1857,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2">
         <v>5</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -1883,19 +1883,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
@@ -1909,19 +1909,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" s="2">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F18" s="2">
         <v>2</v>
@@ -1935,19 +1935,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D19" s="2">
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F19" s="2">
         <v>2</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -1987,19 +1987,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D21" s="2">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F21" s="2">
         <v>2</v>
@@ -2013,19 +2013,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" s="2">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
@@ -2039,19 +2039,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2">
         <v>6</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
@@ -2065,19 +2065,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" s="2">
         <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F24" s="2">
         <v>1</v>
@@ -2091,19 +2091,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2">
         <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F25" s="2">
         <v>1</v>
@@ -2117,19 +2117,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" s="2">
         <v>6</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
@@ -2143,19 +2143,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" s="2">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
@@ -2169,19 +2169,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
@@ -2195,19 +2195,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
@@ -2247,19 +2247,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" s="2">
         <v>5</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
@@ -2273,19 +2273,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D32" s="2">
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F32" s="2">
         <v>1</v>
@@ -2299,19 +2299,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
@@ -2325,19 +2325,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="2">
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D34" s="2">
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
@@ -2351,19 +2351,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2">
         <v>2</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D35" s="2">
         <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
@@ -2377,19 +2377,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2">
         <v>2</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" s="2">
         <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
@@ -2403,19 +2403,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
         <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D37" s="2">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
@@ -2429,19 +2429,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2">
         <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" s="2">
         <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
@@ -2455,19 +2455,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2">
         <v>2</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D39" s="2">
         <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -2481,19 +2481,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2">
         <v>2</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" s="2">
         <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -2507,19 +2507,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="2">
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" s="2">
         <v>5</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
@@ -2533,19 +2533,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2">
         <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -2559,19 +2559,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" s="2">
         <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -2585,19 +2585,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2">
         <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2">
         <v>3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -2611,19 +2611,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="2">
         <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D45" s="2">
         <v>4</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -2637,19 +2637,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="2">
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -2663,19 +2663,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="2">
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2">
         <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -2689,19 +2689,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" s="2">
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" s="2">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -2715,19 +2715,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2">
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" s="2">
         <v>7</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F49" s="2">
         <v>1</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" s="2">
         <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2">
         <v>6</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F50" s="2">
         <v>1</v>
@@ -2767,19 +2767,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" s="2">
         <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" s="2">
         <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F51" s="2">
         <v>1</v>
@@ -2793,19 +2793,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="2">
         <v>4</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D52" s="2">
         <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F52" s="2">
         <v>1</v>
@@ -2819,19 +2819,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="2">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D53" s="2">
         <v>6</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
@@ -2845,19 +2845,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" s="2">
         <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D54" s="2">
         <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F54" s="2">
         <v>2</v>
@@ -2871,19 +2871,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="2">
         <v>4</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D55" s="2">
         <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F55" s="2">
         <v>1</v>
@@ -2897,19 +2897,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="2">
         <v>4</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D56" s="2">
         <v>8</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F56" s="2">
         <v>2</v>
@@ -2923,19 +2923,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" s="2">
         <v>4</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D57" s="2">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F57" s="2">
         <v>2</v>
@@ -2949,19 +2949,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="2">
         <v>4</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D58" s="2">
         <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F58" s="2">
         <v>2</v>
@@ -2975,19 +2975,19 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="2">
         <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="2">
         <v>7</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F59" s="2">
         <v>2</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="2">
         <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D60" s="2">
         <v>7</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F60" s="2">
         <v>2</v>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" s="2">
         <v>4</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" s="2">
         <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F61" s="2">
         <v>1</v>
@@ -3053,19 +3053,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="2">
         <v>4</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D62" s="2">
         <v>6</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F62" s="2">
         <v>1</v>
@@ -3079,19 +3079,19 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D63" s="2">
         <v>6</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F63" s="2">
         <v>2</v>
@@ -3105,19 +3105,19 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="2">
         <v>4</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D64" s="2">
         <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F64" s="2">
         <v>1</v>
@@ -3131,19 +3131,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" s="2">
         <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D65" s="2">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F65" s="2">
         <v>3</v>
@@ -3157,19 +3157,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2">
         <v>4</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" s="2">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F66" s="2">
         <v>1</v>
@@ -3183,19 +3183,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2">
         <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D67" s="2">
         <v>2</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -3209,19 +3209,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2">
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D68" s="2">
         <v>5</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F68" s="2">
         <v>5</v>
@@ -3235,19 +3235,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2">
         <v>1</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D69" s="2">
         <v>1</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F69" s="2">
         <v>6</v>
@@ -3261,19 +3261,19 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2">
         <v>2</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D70" s="2">
         <v>6</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" s="2">
         <v>2</v>
@@ -3287,19 +3287,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2">
         <v>2</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D71" s="2">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F71" s="2">
         <v>5</v>
@@ -3313,19 +3313,19 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2">
         <v>2</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2">
         <v>8</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F72" s="2">
         <v>4</v>
@@ -3339,19 +3339,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2">
         <v>2</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D73" s="2">
         <v>9</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F73" s="2">
         <v>5</v>
@@ -3365,19 +3365,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2">
         <v>2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D74" s="2">
         <v>6</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F74" s="2">
         <v>4</v>
@@ -3391,19 +3391,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" s="2">
         <v>2</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D75" s="2">
         <v>6</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -3417,19 +3417,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" s="2">
         <v>2</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D76" s="2">
         <v>7</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F76" s="2">
         <v>3</v>
@@ -3443,19 +3443,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" s="2">
         <v>3</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D77" s="2">
         <v>2</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F77" s="2">
         <v>2</v>
@@ -3469,19 +3469,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" s="2">
         <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D78" s="2">
         <v>3</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F78" s="2">
         <v>3</v>
@@ -3495,19 +3495,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" s="2">
         <v>3</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D79" s="2">
         <v>3</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F79" s="2">
         <v>2</v>
@@ -3521,19 +3521,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" s="2">
         <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D80" s="2">
         <v>4</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F80" s="2">
         <v>2</v>
@@ -3547,19 +3547,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" s="2">
         <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F81" s="2">
         <v>4</v>
@@ -3573,19 +3573,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" s="2">
         <v>3</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D82" s="2">
         <v>2</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F82" s="2">
         <v>2</v>
@@ -3599,19 +3599,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" s="2">
         <v>3</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D83" s="2">
         <v>5</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F83" s="2">
         <v>4</v>
@@ -3625,19 +3625,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" s="2">
         <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D84" s="2">
         <v>5</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F84" s="2">
         <v>2</v>
@@ -3651,19 +3651,19 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" s="2">
         <v>3</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D85" s="2">
         <v>3</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F85" s="2">
         <v>2</v>
@@ -3677,19 +3677,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" s="2">
         <v>3</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D86" s="2">
         <v>4</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F86" s="2">
         <v>3</v>
@@ -3703,19 +3703,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" s="2">
         <v>4</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D87" s="2">
         <v>8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F87" s="2">
         <v>1</v>
@@ -3729,19 +3729,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B88" s="2">
         <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="2">
         <v>3</v>
@@ -3755,19 +3755,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B89" s="2">
         <v>1</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D89" s="2">
         <v>3</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F89" s="2">
         <v>7</v>
@@ -3781,19 +3781,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B90" s="2">
         <v>1</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D90" s="2">
         <v>4</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F90" s="2">
         <v>3</v>
@@ -3807,19 +3807,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B91" s="2">
         <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D91" s="2">
         <v>3</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F91" s="2">
         <v>4</v>
@@ -3833,19 +3833,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B92" s="2">
         <v>1</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2">
         <v>2</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F92" s="2">
         <v>2</v>
@@ -3859,19 +3859,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B93" s="2">
         <v>2</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D93" s="2">
         <v>7</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F93" s="2">
         <v>2</v>
@@ -3885,19 +3885,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94" s="2">
         <v>3</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D94" s="2">
         <v>4</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F94" s="2">
         <v>2</v>
@@ -3911,19 +3911,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B95" s="2">
         <v>2</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D95" s="2">
         <v>7</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F95" s="2">
         <v>2</v>
@@ -3937,19 +3937,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B96" s="2">
         <v>2</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D96" s="2">
         <v>10</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F96" s="2">
         <v>3</v>
@@ -3963,19 +3963,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B97" s="2">
         <v>2</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D97" s="2">
         <v>6</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F97" s="2">
         <v>2</v>
@@ -3989,19 +3989,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B98" s="2">
         <v>2</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D98" s="2">
         <v>9</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F98" s="2">
         <v>2</v>
@@ -4015,19 +4015,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B99" s="2">
         <v>2</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D99" s="2">
         <v>8</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F99" s="2">
         <v>2</v>
@@ -4041,19 +4041,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B100" s="2">
         <v>2</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D100" s="2">
         <v>9</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F100" s="2">
         <v>3</v>
@@ -4067,19 +4067,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B101" s="2">
         <v>2</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D101" s="2">
         <v>3</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F101" s="2">
         <v>1</v>
@@ -4093,19 +4093,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B102" s="2">
         <v>2</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D102" s="2">
         <v>8</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F102" s="2">
         <v>1</v>
@@ -4119,19 +4119,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B103" s="2">
         <v>2</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F103" s="2">
         <v>1</v>
@@ -4145,19 +4145,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B104" s="2">
         <v>4</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D104" s="2">
         <v>10</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F104" s="2">
         <v>1</v>
@@ -4171,19 +4171,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105" s="2">
         <v>3</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D105" s="2">
         <v>3</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F105" s="2">
         <v>3</v>
@@ -4197,19 +4197,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B106" s="2">
         <v>3</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D106" s="2">
         <v>7</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F106" s="2">
         <v>1</v>
@@ -4223,19 +4223,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B107" s="2">
         <v>3</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D107" s="2">
         <v>6</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F107" s="2">
         <v>1</v>
@@ -4249,19 +4249,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B108" s="2">
         <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D108" s="2">
         <v>6</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F108" s="2">
         <v>1</v>
@@ -4275,19 +4275,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B109" s="2">
         <v>3</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D109" s="2">
         <v>4</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F109" s="2">
         <v>1</v>
@@ -4301,19 +4301,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B110" s="2">
         <v>3</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D110" s="2">
         <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F110" s="2">
         <v>1</v>
@@ -4327,19 +4327,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B111" s="2">
         <v>4</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D111" s="2">
         <v>1</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F111" s="2">
         <v>1</v>
@@ -4353,19 +4353,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B112" s="2">
         <v>3</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D112" s="2">
         <v>1</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F112" s="2">
         <v>2</v>
@@ -4379,19 +4379,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B113" s="2">
         <v>4</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D113" s="2">
         <v>8</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F113" s="2">
         <v>1</v>
@@ -4405,19 +4405,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B114" s="2">
         <v>4</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D114" s="2">
         <v>8</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F114" s="2">
         <v>2</v>
@@ -4431,19 +4431,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B115" s="2">
         <v>4</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D115" s="2">
         <v>6</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F115" s="2">
         <v>2</v>
@@ -4457,19 +4457,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B116" s="2">
         <v>4</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D116" s="2">
         <v>7</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F116" s="2">
         <v>1</v>
@@ -4483,19 +4483,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B117" s="2">
         <v>4</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D117" s="2">
         <v>2</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -4509,19 +4509,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B118" s="2">
         <v>4</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D118" s="2">
         <v>5</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F118" s="2">
         <v>1</v>
@@ -4535,19 +4535,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B119" s="2">
         <v>4</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D119" s="2">
         <v>4</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F119" s="2">
         <v>1</v>
@@ -4561,19 +4561,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B120" s="2">
         <v>4</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D120" s="2">
         <v>10</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -4587,19 +4587,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121" s="2">
         <v>1</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D121" s="2">
         <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F121" s="2">
         <v>2</v>
@@ -4613,19 +4613,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B122" s="2">
         <v>1</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122" s="2">
         <v>3</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F122" s="2">
         <v>1</v>
@@ -4639,19 +4639,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B123" s="2">
         <v>1</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D123" s="2">
         <v>5</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F123" s="2">
         <v>2</v>
@@ -4665,19 +4665,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B124" s="2">
         <v>1</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="2">
         <v>2</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F124" s="2">
         <v>3</v>
@@ -4691,19 +4691,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B125" s="2">
         <v>1</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D125" s="2">
         <v>2</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F125" s="2">
         <v>3</v>
@@ -4717,19 +4717,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B126" s="2">
         <v>2</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D126" s="2">
         <v>7</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F126" s="2">
         <v>2</v>
@@ -4743,19 +4743,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B127" s="2">
         <v>2</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D127" s="2">
         <v>8</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F127" s="2">
         <v>3</v>
@@ -4769,19 +4769,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B128" s="2">
         <v>2</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D128" s="2">
         <v>6</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F128" s="2">
         <v>4</v>
@@ -4795,19 +4795,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B129" s="2">
         <v>2</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D129" s="2">
         <v>10</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F129" s="2">
         <v>3</v>
@@ -4821,19 +4821,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B130" s="2">
         <v>2</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D130" s="2">
         <v>7</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F130" s="2">
         <v>2</v>
@@ -4847,19 +4847,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B131" s="2">
         <v>2</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D131" s="2">
         <v>9</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F131" s="2">
         <v>2</v>
@@ -4873,19 +4873,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B132" s="2">
         <v>2</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D132" s="2">
         <v>10</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F132" s="2">
         <v>3</v>
@@ -4899,19 +4899,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B133" s="2">
         <v>3</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D133" s="2">
         <v>2</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F133" s="2">
         <v>3</v>
@@ -4925,19 +4925,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B134" s="2">
         <v>3</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D134" s="2">
         <v>4</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F134" s="2">
         <v>3</v>
@@ -4951,19 +4951,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B135" s="2">
         <v>3</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D135" s="2">
         <v>3</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F135" s="2">
         <v>2</v>
@@ -4977,19 +4977,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B136" s="2">
         <v>3</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D136" s="2">
         <v>2</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F136" s="2">
         <v>2</v>
@@ -5003,19 +5003,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B137" s="2">
         <v>3</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -5029,19 +5029,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B138" s="2">
         <v>3</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F138" s="2">
         <v>2</v>
@@ -5055,19 +5055,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B139" s="2">
         <v>3</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D139" s="2">
         <v>4</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F139" s="2">
         <v>1</v>
@@ -5081,19 +5081,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B140" s="2">
         <v>3</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D140" s="2">
         <v>5</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F140" s="2">
         <v>2</v>
@@ -5107,19 +5107,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B141" s="2">
         <v>3</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D141" s="2">
         <v>3</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F141" s="2">
         <v>1</v>
@@ -5133,19 +5133,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B142" s="2">
         <v>4</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D142" s="2">
         <v>6</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F142" s="2">
         <v>2</v>
@@ -5159,19 +5159,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B143" s="2">
         <v>4</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D143" s="2">
         <v>7</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F143" s="2">
         <v>1</v>
@@ -5185,19 +5185,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B144" s="2">
         <v>4</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D144" s="2">
         <v>7</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F144" s="2">
         <v>1</v>
@@ -5211,19 +5211,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B145" s="2">
         <v>4</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D145" s="2">
         <v>6</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F145" s="2">
         <v>1</v>
@@ -5237,19 +5237,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B146" s="2">
         <v>4</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D146" s="2">
         <v>7</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -5263,19 +5263,19 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B147" s="2">
         <v>4</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D147" s="2">
         <v>10</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F147" s="2">
         <v>1</v>
@@ -5289,19 +5289,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B148" s="2">
         <v>4</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D148" s="2">
         <v>8</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F148" s="2">
         <v>1</v>
@@ -5315,19 +5315,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B149" s="2">
         <v>4</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D149" s="2">
         <v>7</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F149" s="2">
         <v>1</v>
@@ -5341,19 +5341,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B150" s="2">
         <v>4</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D150" s="2">
         <v>8</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F150" s="2">
         <v>1</v>
@@ -5367,19 +5367,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B151" s="2">
         <v>4</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D151" s="2">
         <v>9</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F151" s="2">
         <v>1</v>
@@ -5393,19 +5393,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B152" s="2">
         <v>1</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D152" s="2">
         <v>3</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F152" s="2">
         <v>1</v>
@@ -5419,19 +5419,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B153" s="2">
         <v>1</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F153" s="2">
         <v>1</v>
@@ -5445,19 +5445,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B154" s="2">
         <v>1</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D154" s="2">
         <v>4</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F154" s="2">
         <v>1</v>
@@ -5471,19 +5471,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B155" s="2">
         <v>2</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D155" s="2">
         <v>10</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F155" s="2">
         <v>1</v>
@@ -5497,19 +5497,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B156" s="2">
         <v>2</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D156" s="2">
         <v>6</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F156" s="2">
         <v>1</v>
@@ -5523,19 +5523,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B157" s="2">
         <v>2</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D157" s="2">
         <v>7</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
@@ -5549,19 +5549,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B158" s="2">
         <v>2</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D158" s="2">
         <v>9</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F158" s="2">
         <v>1</v>
@@ -5575,19 +5575,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B159" s="2">
         <v>2</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D159" s="2">
         <v>8</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F159" s="2">
         <v>1</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B160" s="2">
         <v>3</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F160" s="2">
         <v>1</v>
@@ -5627,19 +5627,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B161" s="2">
         <v>3</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D161" s="2">
         <v>2</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F161" s="2">
         <v>1</v>
@@ -5653,19 +5653,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B162" s="2">
         <v>3</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D162" s="2">
         <v>5</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F162" s="2">
         <v>1</v>
@@ -5679,19 +5679,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B163" s="2">
         <v>3</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D163" s="2">
         <v>4</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -5705,19 +5705,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B164" s="2">
         <v>3</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D164" s="2">
         <v>3</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F164" s="2">
         <v>1</v>
@@ -5731,19 +5731,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B165" s="2">
         <v>3</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F165" s="2">
         <v>1</v>
@@ -5757,19 +5757,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B166" s="2">
         <v>3</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D166" s="2">
         <v>3</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F166" s="2">
         <v>1</v>
@@ -5783,19 +5783,19 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B167" s="2">
         <v>4</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D167" s="2">
         <v>8</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F167" s="2">
         <v>1</v>
@@ -5809,19 +5809,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B168" s="2">
         <v>4</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D168" s="2">
         <v>10</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F168" s="2">
         <v>1</v>
@@ -5835,19 +5835,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B169" s="2">
         <v>4</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D169" s="2">
         <v>9</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F169" s="2">
         <v>1</v>
@@ -5861,19 +5861,19 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B170" s="2">
         <v>4</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D170" s="2">
         <v>6</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F170" s="2">
         <v>1</v>
@@ -5887,19 +5887,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B171" s="2">
         <v>4</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D171" s="2">
         <v>7</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F171" s="2">
         <v>1</v>
@@ -5913,19 +5913,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B172" s="2">
         <v>1</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D172" s="2">
         <v>1</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F172" s="2">
         <v>2</v>
@@ -5939,19 +5939,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B173" s="2">
         <v>1</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D173" s="2">
         <v>5</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F173" s="2">
         <v>2</v>
@@ -5965,19 +5965,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B174" s="2">
         <v>1</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D174" s="2">
         <v>5</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F174" s="2">
         <v>2</v>
@@ -5991,19 +5991,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B175" s="2">
         <v>1</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D175" s="2">
         <v>3</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F175" s="2">
         <v>2</v>
@@ -6017,19 +6017,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B176" s="2">
         <v>1</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D176" s="2">
         <v>1</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F176" s="2">
         <v>4</v>
@@ -6043,19 +6043,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B177" s="2">
         <v>1</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D177" s="2">
         <v>6</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F177" s="2">
         <v>3</v>
@@ -6069,19 +6069,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B178" s="2">
         <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D178" s="2">
         <v>8</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F178" s="2">
         <v>3</v>
@@ -6095,19 +6095,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B179" s="2">
         <v>1</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D179" s="2">
         <v>7</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F179" s="2">
         <v>3</v>
@@ -6121,19 +6121,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B180" s="2">
         <v>2</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D180" s="2">
         <v>5</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F180" s="2">
         <v>3</v>
@@ -6147,19 +6147,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B181" s="2">
         <v>2</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D181" s="2">
         <v>4</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F181" s="2">
         <v>3</v>
@@ -6173,19 +6173,19 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B182" s="2">
         <v>2</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D182" s="2">
         <v>1</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F182" s="2">
         <v>4</v>
@@ -6199,19 +6199,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B183" s="2">
         <v>2</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D183" s="2">
         <v>6</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F183" s="2">
         <v>3</v>
@@ -6225,19 +6225,19 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B184" s="2">
         <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D184" s="2">
         <v>7</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F184" s="2">
         <v>3</v>
@@ -6251,19 +6251,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B185" s="2">
         <v>2</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D185" s="2">
         <v>8</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F185" s="2">
         <v>2</v>
@@ -6277,19 +6277,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B186" s="2">
         <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D186" s="2">
         <v>1</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F186" s="2">
         <v>4</v>
@@ -6303,19 +6303,19 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B187" s="2">
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D187" s="2">
         <v>5</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F187" s="2">
         <v>3</v>
@@ -6329,19 +6329,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B188" s="2">
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D188" s="2">
         <v>8</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F188" s="2">
         <v>2</v>
@@ -6355,19 +6355,19 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B189" s="2">
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D189" s="2">
         <v>7</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F189" s="2">
         <v>3</v>
@@ -6381,19 +6381,19 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B190" s="2">
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D190" s="2">
         <v>3</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F190" s="2">
         <v>3</v>
@@ -6407,19 +6407,19 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B191" s="2">
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D191" s="2">
         <v>4</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F191" s="2">
         <v>1</v>
@@ -6433,19 +6433,19 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B192" s="2">
         <v>3</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D192" s="2">
         <v>4</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F192" s="2">
         <v>1</v>
@@ -6459,19 +6459,19 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B193" s="2">
         <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D193" s="2">
         <v>4</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F193" s="2">
         <v>1</v>
@@ -6485,19 +6485,19 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B194" s="2">
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D194" s="2">
         <v>4</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F194" s="2">
         <v>1</v>
@@ -6511,19 +6511,19 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B195" s="2">
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D195" s="2">
         <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F195" s="2">
         <v>1</v>
@@ -6537,19 +6537,19 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B196" s="2">
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D196" s="2">
         <v>2</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F196" s="2">
         <v>1</v>
@@ -6563,19 +6563,19 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B197" s="2">
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D197" s="2">
         <v>2</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F197" s="2">
         <v>1</v>
@@ -6589,19 +6589,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B198" s="2">
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D198" s="2">
         <v>5</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F198" s="2">
         <v>1</v>
@@ -6615,19 +6615,19 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B199" s="2">
         <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D199" s="2">
         <v>6</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F199" s="2">
         <v>1</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B200" s="2">
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D200" s="2">
         <v>7</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F200" s="2">
         <v>1</v>
@@ -6667,19 +6667,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B201" s="2">
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D201" s="2">
         <v>4</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F201" s="2">
         <v>1</v>
@@ -6693,19 +6693,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B202" s="2">
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D202" s="2">
         <v>1</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F202" s="2">
         <v>1</v>
@@ -6719,19 +6719,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B203" s="2">
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D203" s="2">
         <v>7</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F203" s="2">
         <v>1</v>
@@ -6745,19 +6745,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B204" s="2">
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D204" s="2">
         <v>1</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F204" s="2">
         <v>1</v>
@@ -6771,19 +6771,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B205" s="2">
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D205" s="2">
         <v>2</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F205" s="2">
         <v>1</v>
@@ -6797,19 +6797,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206" s="2">
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D206" s="2">
         <v>2</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F206" s="2">
         <v>1</v>
@@ -6823,19 +6823,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B207" s="2">
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D207" s="2">
         <v>6</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F207" s="2">
         <v>1</v>
@@ -6849,19 +6849,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B208" s="2">
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D208" s="2">
         <v>8</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F208" s="2">
         <v>1</v>
@@ -6875,19 +6875,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B209" s="2">
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D209" s="2">
         <v>4</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F209" s="2">
         <v>1</v>
@@ -6901,19 +6901,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B210" s="2">
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D210" s="2">
         <v>5</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F210" s="2">
         <v>1</v>
@@ -6927,19 +6927,19 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B211" s="2">
         <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F211" s="2">
         <v>5</v>
@@ -6953,19 +6953,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B212" s="2">
         <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D212" s="2">
         <v>4</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F212" s="2">
         <v>5</v>
@@ -6979,19 +6979,19 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B213" s="2">
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D213" s="2">
         <v>5</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F213" s="2">
         <v>2</v>
@@ -7005,19 +7005,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B214" s="2">
         <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D214" s="2">
         <v>1</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F214" s="2">
         <v>3</v>
@@ -7031,19 +7031,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B215" s="2">
         <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D215" s="2">
         <v>5</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F215" s="2">
         <v>3</v>
@@ -7057,19 +7057,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B216" s="2">
         <v>2</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D216" s="2">
         <v>9</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F216" s="2">
         <v>3</v>
@@ -7083,19 +7083,19 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B217" s="2">
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D217" s="2">
         <v>8</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F217" s="2">
         <v>1</v>

--- a/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
+++ b/data/department_schedules_midterms/faculty_schedule_manuel_midterms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB858EF-1756-4B2F-884F-4E870F4EF3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F4DAFA-893A-4A61-A19E-5D89FF9D6371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35520" yWindow="13725" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1459,7 +1459,7 @@
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.08984375" customWidth="1"/>
     <col min="6" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="15.6328125" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
